--- a/erp-server/erp-server-file/src/main/resources/excel/wms/transferInfo.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/transferInfo.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>调拨单号</t>
   </si>
@@ -62,9 +62,15 @@
     <t>调出仓库</t>
   </si>
   <si>
+    <t>调出库存状态</t>
+  </si>
+  <si>
     <t>调入仓库</t>
   </si>
   <si>
+    <t>调入库存状态</t>
+  </si>
+  <si>
     <t>调出仓位</t>
   </si>
   <si>
@@ -116,7 +122,13 @@
     <t>{.outWarehouseName}</t>
   </si>
   <si>
+    <t>{.outInventoryStatusName}</t>
+  </si>
+  <si>
     <t>{.inWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.inInventoryStatusName}</t>
   </si>
   <si>
     <t>{.outWarehouseLocation}</t>
@@ -1105,7 +1117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="16.625" customWidth="1"/>
@@ -1116,16 +1128,18 @@
     <col min="7" max="7" width="18.375" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
     <col min="9" max="9" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="29.875" customWidth="1"/>
-    <col min="13" max="14" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="20.875" customWidth="1"/>
-    <col min="16" max="16" width="12.625" customWidth="1"/>
-    <col min="17" max="17" width="9.75" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
+    <col min="11" max="11" width="21.5" customWidth="1"/>
+    <col min="12" max="12" width="28.25" customWidth="1"/>
+    <col min="13" max="13" width="20.375" customWidth="1"/>
+    <col min="14" max="14" width="27.125" customWidth="1"/>
+    <col min="15" max="16" width="14.25" customWidth="1"/>
+    <col min="17" max="17" width="20.875" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="19" max="19" width="9.75" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1180,61 +1194,73 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
